--- a/data/trans_bre/P3A_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 8,5</t>
+          <t>-13,99; 8,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 16,44</t>
+          <t>-4,88; 16,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 8,0</t>
+          <t>-10,88; 8,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 14,84</t>
+          <t>-3,71; 15,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,94; 28,92</t>
+          <t>-34,68; 29,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 62,36</t>
+          <t>-12,62; 66,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-35,44; 40,37</t>
+          <t>-35,7; 42,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 19,34</t>
+          <t>-3,95; 19,57</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 9,8</t>
+          <t>-4,86; 10,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 11,96</t>
+          <t>-3,85; 12,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 2,3</t>
+          <t>-13,19; 1,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,43; -0,25</t>
+          <t>-13,72; -0,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 34,14</t>
+          <t>-13,04; 36,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 45,64</t>
+          <t>-11,88; 45,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,28; 7,51</t>
+          <t>-35,16; 5,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,79; -0,45</t>
+          <t>-14,86; -0,75</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 16,57</t>
+          <t>-5,98; 16,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 12,71</t>
+          <t>-8,38; 13,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 11,62</t>
+          <t>-7,81; 11,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 12,65</t>
+          <t>0,17; 12,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 51,38</t>
+          <t>-15,93; 52,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,77; 45,96</t>
+          <t>-22,54; 48,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 39,68</t>
+          <t>-19,33; 36,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 16,07</t>
+          <t>0,28; 16,41</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 3,71</t>
+          <t>-14,11; 3,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,11; -0,32</t>
+          <t>-20,08; -0,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 13,08</t>
+          <t>-7,0; 13,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 4,16</t>
+          <t>-9,5; 4,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,41; 12,19</t>
+          <t>-34,44; 8,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,03; -0,32</t>
+          <t>-42,91; -0,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 43,23</t>
+          <t>-17,37; 46,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 4,97</t>
+          <t>-10,86; 5,22</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 4,04</t>
+          <t>-4,84; 4,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 5,82</t>
+          <t>-4,21; 5,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 4,3</t>
+          <t>-4,98; 3,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 3,36</t>
+          <t>-4,44; 3,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 12,01</t>
+          <t>-12,89; 12,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 19,02</t>
+          <t>-11,82; 17,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 13,75</t>
+          <t>-14,32; 13,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 3,94</t>
+          <t>-5,08; 3,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 8,92</t>
+          <t>-12,96; 9,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 16,75</t>
+          <t>-2,61; 18,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 8,92</t>
+          <t>-10,34; 9,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 15,01</t>
+          <t>-4,07; 16,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,68; 29,79</t>
+          <t>-32,11; 34,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 66,81</t>
+          <t>-7,87; 72,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-35,7; 42,98</t>
+          <t>-33,94; 45,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 19,57</t>
+          <t>-4,44; 21,29</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 10,47</t>
+          <t>-5,29; 10,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 12,14</t>
+          <t>-4,34; 12,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 1,81</t>
+          <t>-13,68; 1,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,72; -0,65</t>
+          <t>-13,83; -0,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 36,08</t>
+          <t>-14,21; 35,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 45,93</t>
+          <t>-13,48; 47,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,16; 5,99</t>
+          <t>-35,92; 6,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,86; -0,75</t>
+          <t>-15,14; -0,48</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 16,68</t>
+          <t>-6,29; 16,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 13,3</t>
+          <t>-9,45; 12,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 11,16</t>
+          <t>-7,3; 11,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 12,68</t>
+          <t>-0,54; 12,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 52,08</t>
+          <t>-16,1; 49,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,54; 48,68</t>
+          <t>-24,41; 45,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-19,33; 36,51</t>
+          <t>-19,09; 39,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 16,41</t>
+          <t>-0,6; 16,02</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 3,14</t>
+          <t>-14,63; 2,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,08; -0,39</t>
+          <t>-19,42; 0,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 13,41</t>
+          <t>-7,36; 13,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 4,49</t>
+          <t>-9,22; 5,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,44; 8,93</t>
+          <t>-34,52; 9,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,91; -0,81</t>
+          <t>-42,68; -0,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 46,54</t>
+          <t>-17,34; 48,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 5,22</t>
+          <t>-10,39; 5,9</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 4,03</t>
+          <t>-4,91; 4,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 5,55</t>
+          <t>-4,1; 5,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 3,99</t>
+          <t>-5,32; 3,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 3,28</t>
+          <t>-4,2; 3,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 12,07</t>
+          <t>-12,93; 13,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 17,6</t>
+          <t>-11,58; 17,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 13,0</t>
+          <t>-15,15; 12,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 3,87</t>
+          <t>-4,82; 3,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,3</t>
+          <t>6,85</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 9,95</t>
+          <t>-14,57; 8,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 18,29</t>
+          <t>-5,42; 16,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 9,11</t>
+          <t>-10,76; 8,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 16,18</t>
+          <t>-2,2; 16,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 34,34</t>
+          <t>-34,94; 28,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 72,21</t>
+          <t>-14,4; 62,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-33,94; 45,65</t>
+          <t>-35,44; 40,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 21,29</t>
+          <t>-2,46; 22,8</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,71</t>
+          <t>-5,22</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-7,49%</t>
+          <t>-5,84%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 10,43</t>
+          <t>-5,69; 9,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 12,0</t>
+          <t>-4,98; 11,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 1,98</t>
+          <t>-13,1; 2,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,83; -0,31</t>
+          <t>-11,42; 1,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 35,61</t>
+          <t>-14,84; 34,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 47,0</t>
+          <t>-15,1; 45,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,92; 6,34</t>
+          <t>-34,28; 7,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,14; -0,48</t>
+          <t>-12,49; 1,83</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,19</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 16,04</t>
+          <t>-6,85; 16,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 12,84</t>
+          <t>-9,76; 12,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 11,89</t>
+          <t>-7,41; 11,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 12,69</t>
+          <t>-0,35; 12,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 49,99</t>
+          <t>-17,13; 51,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,41; 45,13</t>
+          <t>-26,77; 45,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 39,17</t>
+          <t>-18,7; 39,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 16,02</t>
+          <t>-0,31; 16,6</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,16</t>
+          <t>-1,02</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-2,49%</t>
+          <t>-1,17%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 2,95</t>
+          <t>-13,97; 3,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 0,04</t>
+          <t>-19,11; -0,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 13,87</t>
+          <t>-6,82; 13,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 5,04</t>
+          <t>-7,09; 4,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 9,22</t>
+          <t>-33,41; 12,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,68; -0,4</t>
+          <t>-41,03; -0,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 48,65</t>
+          <t>-17,37; 43,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 5,9</t>
+          <t>-7,94; 4,92</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-0,43%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 4,48</t>
+          <t>-5,66; 4,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 5,45</t>
+          <t>-4,27; 5,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 3,91</t>
+          <t>-5,25; 4,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 3,3</t>
+          <t>-2,75; 3,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 13,32</t>
+          <t>-14,66; 12,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 17,26</t>
+          <t>-11,83; 19,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 12,08</t>
+          <t>-14,77; 13,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 3,91</t>
+          <t>-3,11; 4,66</t>
         </is>
       </c>
     </row>
